--- a/uploadedFiles/Questionnaire/baa2014UploadQuestionnairePeggyTest1.xlsx
+++ b/uploadedFiles/Questionnaire/baa2014UploadQuestionnairePeggyTest1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\john\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\costco majors\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-15" windowWidth="11910" windowHeight="9435"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8595"/>
   </bookViews>
   <sheets>
     <sheet name="surveyQuestion" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="100">
   <si>
     <t>Page</t>
   </si>
@@ -297,6 +297,9 @@
   </si>
   <si>
     <t>3720=0&amp;3720=0:3722;</t>
+  </si>
+  <si>
+    <t>YN_WARNING_N</t>
   </si>
   <si>
     <t>3709=3&amp;3709=3:3722;</t>
@@ -1413,7 +1416,7 @@
         <v>66</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F2" s="23" t="s">
         <v>25</v>
@@ -1559,7 +1562,7 @@
         <v>39</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G4" s="23">
         <v>0</v>
@@ -1600,7 +1603,7 @@
         <v>78</v>
       </c>
       <c r="S4" s="32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="V4" s="21">
         <v>0</v>
@@ -1700,7 +1703,7 @@
         <v>43</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G6" s="23">
         <v>0</v>
@@ -1742,7 +1745,7 @@
         <v>78</v>
       </c>
       <c r="S6" s="32" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V6" s="21">
         <v>0</v>
@@ -1842,7 +1845,7 @@
         <v>47</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G8" s="23">
         <v>0</v>
@@ -2050,7 +2053,7 @@
         <v>53</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G11" s="23">
         <v>0</v>
@@ -2258,7 +2261,7 @@
         <v>59</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G14" s="23">
         <v>0</v>
@@ -2300,7 +2303,7 @@
         <v>78</v>
       </c>
       <c r="S14" s="32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V14" s="21">
         <v>0</v>
@@ -2374,10 +2377,10 @@
         <v>88</v>
       </c>
       <c r="T15" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="V15" s="21">
-        <v>1</v>
+        <v>98</v>
+      </c>
+      <c r="V15" s="21" t="s">
+        <v>89</v>
       </c>
       <c r="W15" s="19" t="s">
         <v>23</v>
@@ -2403,7 +2406,7 @@
         <v>63</v>
       </c>
       <c r="F16" s="35" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G16" s="23">
         <v>0</v>
